--- a/output/yearly_population_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_16_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6313</v>
+        <v>6208</v>
       </c>
       <c r="C2" t="n">
-        <v>6470</v>
+        <v>12423</v>
       </c>
       <c r="D2" t="n">
-        <v>27789</v>
+        <v>35038</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3957</v>
+        <v>3791</v>
       </c>
       <c r="C3" t="n">
-        <v>5359</v>
+        <v>5638</v>
       </c>
       <c r="D3" t="n">
-        <v>17113</v>
+        <v>21584</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3032</v>
+        <v>3126</v>
       </c>
       <c r="C4" t="n">
-        <v>5025</v>
+        <v>5546</v>
       </c>
       <c r="D4" t="n">
-        <v>7385</v>
+        <v>11523</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1909</v>
+        <v>2064</v>
       </c>
       <c r="C5" t="n">
-        <v>4963</v>
+        <v>4771</v>
       </c>
       <c r="D5" t="n">
-        <v>2600</v>
+        <v>4326</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>973</v>
+        <v>1192</v>
       </c>
       <c r="C6" t="n">
-        <v>3719</v>
+        <v>3102</v>
       </c>
       <c r="D6" t="n">
-        <v>1144</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>562</v>
       </c>
       <c r="C7" t="n">
-        <v>2131</v>
+        <v>1722</v>
       </c>
       <c r="D7" t="n">
-        <v>647</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="C8" t="n">
-        <v>993</v>
+        <v>832</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -934,10 +934,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D13" t="n">
         <v>124</v>
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8520</v>
+        <v>8165</v>
       </c>
       <c r="C2" t="n">
-        <v>4700</v>
+        <v>7972</v>
       </c>
       <c r="D2" t="n">
-        <v>32966</v>
+        <v>29441</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4042</v>
+        <v>3907</v>
       </c>
       <c r="C3" t="n">
-        <v>5211</v>
+        <v>7539</v>
       </c>
       <c r="D3" t="n">
-        <v>17356</v>
+        <v>21890</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2924</v>
+        <v>2910</v>
       </c>
       <c r="C4" t="n">
-        <v>5026</v>
+        <v>5472</v>
       </c>
       <c r="D4" t="n">
-        <v>8583</v>
+        <v>12718</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2101</v>
+        <v>2232</v>
       </c>
       <c r="C5" t="n">
-        <v>4840</v>
+        <v>4960</v>
       </c>
       <c r="D5" t="n">
-        <v>3255</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1236</v>
+        <v>1402</v>
       </c>
       <c r="C6" t="n">
-        <v>4232</v>
+        <v>3748</v>
       </c>
       <c r="D6" t="n">
-        <v>1327</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>592</v>
+        <v>728</v>
       </c>
       <c r="C7" t="n">
-        <v>2794</v>
+        <v>2302</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="C8" t="n">
-        <v>1472</v>
+        <v>1181</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>633</v>
+        <v>550</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="D10" t="n">
         <v>247</v>
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8644</v>
+        <v>9798</v>
       </c>
       <c r="C2" t="n">
-        <v>12517</v>
+        <v>8141</v>
       </c>
       <c r="D2" t="n">
-        <v>33130</v>
+        <v>43605</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4691</v>
+        <v>4449</v>
       </c>
       <c r="C3" t="n">
-        <v>4455</v>
+        <v>6940</v>
       </c>
       <c r="D3" t="n">
-        <v>18118</v>
+        <v>21605</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2868</v>
+        <v>2801</v>
       </c>
       <c r="C4" t="n">
-        <v>4951</v>
+        <v>6139</v>
       </c>
       <c r="D4" t="n">
-        <v>9502</v>
+        <v>13441</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2178</v>
+        <v>2224</v>
       </c>
       <c r="C5" t="n">
-        <v>4816</v>
+        <v>5010</v>
       </c>
       <c r="D5" t="n">
-        <v>3923</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1425</v>
+        <v>1561</v>
       </c>
       <c r="C6" t="n">
-        <v>4393</v>
+        <v>4145</v>
       </c>
       <c r="D6" t="n">
-        <v>1555</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>748</v>
+        <v>878</v>
       </c>
       <c r="C7" t="n">
-        <v>3329</v>
+        <v>2853</v>
       </c>
       <c r="D7" t="n">
-        <v>789</v>
+        <v>909</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>327</v>
+        <v>402</v>
       </c>
       <c r="C8" t="n">
-        <v>1976</v>
+        <v>1575</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="C9" t="n">
-        <v>930</v>
+        <v>767</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8003</v>
+        <v>8908</v>
       </c>
       <c r="C2" t="n">
-        <v>8711</v>
+        <v>5731</v>
       </c>
       <c r="D2" t="n">
-        <v>27373</v>
+        <v>36128</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5361</v>
+        <v>5115</v>
       </c>
       <c r="C3" t="n">
-        <v>7669</v>
+        <v>10095</v>
       </c>
       <c r="D3" t="n">
-        <v>19442</v>
+        <v>23754</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2012</v>
+        <v>2054</v>
       </c>
       <c r="C4" t="n">
-        <v>7285</v>
+        <v>8050</v>
       </c>
       <c r="D4" t="n">
-        <v>8914</v>
+        <v>12845</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1316</v>
+        <v>1442</v>
       </c>
       <c r="C5" t="n">
-        <v>4305</v>
+        <v>4062</v>
       </c>
       <c r="D5" t="n">
-        <v>2578</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>691</v>
+        <v>811</v>
       </c>
       <c r="C6" t="n">
-        <v>3262</v>
+        <v>2795</v>
       </c>
       <c r="D6" t="n">
-        <v>773</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>371</v>
       </c>
       <c r="C7" t="n">
-        <v>1936</v>
+        <v>1543</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>911</v>
+        <v>751</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>399</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4956</v>
+        <v>5321</v>
       </c>
       <c r="C2" t="n">
-        <v>4311</v>
+        <v>2580</v>
       </c>
       <c r="D2" t="n">
-        <v>18952</v>
+        <v>25223</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5557</v>
+        <v>5671</v>
       </c>
       <c r="C3" t="n">
-        <v>7386</v>
+        <v>7479</v>
       </c>
       <c r="D3" t="n">
-        <v>19587</v>
+        <v>24007</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2810</v>
+        <v>2742</v>
       </c>
       <c r="C4" t="n">
-        <v>7516</v>
+        <v>9017</v>
       </c>
       <c r="D4" t="n">
-        <v>10244</v>
+        <v>14272</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1469</v>
+        <v>1575</v>
       </c>
       <c r="C5" t="n">
-        <v>5623</v>
+        <v>5742</v>
       </c>
       <c r="D5" t="n">
-        <v>3364</v>
+        <v>4795</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>830</v>
+        <v>953</v>
       </c>
       <c r="C6" t="n">
-        <v>3780</v>
+        <v>3380</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="C7" t="n">
-        <v>2456</v>
+        <v>1970</v>
       </c>
       <c r="D7" t="n">
-        <v>507</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>1200</v>
+        <v>986</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
+        <v>158</v>
+      </c>
+      <c r="D11" t="n">
         <v>163</v>
-      </c>
-      <c r="D11" t="n">
-        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -2178,10 +2178,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5188</v>
+        <v>6497</v>
       </c>
       <c r="C2" t="n">
-        <v>6199</v>
+        <v>7235</v>
       </c>
       <c r="D2" t="n">
-        <v>14974</v>
+        <v>25880</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4458</v>
+        <v>4692</v>
       </c>
       <c r="C3" t="n">
-        <v>5304</v>
+        <v>4673</v>
       </c>
       <c r="D3" t="n">
-        <v>18184</v>
+        <v>22789</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3425</v>
+        <v>3356</v>
       </c>
       <c r="C4" t="n">
-        <v>7297</v>
+        <v>8105</v>
       </c>
       <c r="D4" t="n">
-        <v>11457</v>
+        <v>15196</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1792</v>
+        <v>1824</v>
       </c>
       <c r="C5" t="n">
-        <v>6378</v>
+        <v>7155</v>
       </c>
       <c r="D5" t="n">
-        <v>4318</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>996</v>
+        <v>1102</v>
       </c>
       <c r="C6" t="n">
-        <v>4594</v>
+        <v>4346</v>
       </c>
       <c r="D6" t="n">
-        <v>1278</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>504</v>
       </c>
       <c r="C7" t="n">
-        <v>3037</v>
+        <v>2568</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>1703</v>
+        <v>1371</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>724</v>
+        <v>598</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3103</v>
+        <v>3915</v>
       </c>
       <c r="C2" t="n">
-        <v>2943</v>
+        <v>3520</v>
       </c>
       <c r="D2" t="n">
-        <v>10466</v>
+        <v>18057</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4466</v>
+        <v>4921</v>
       </c>
       <c r="C3" t="n">
-        <v>5444</v>
+        <v>5365</v>
       </c>
       <c r="D3" t="n">
-        <v>17442</v>
+        <v>22599</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3759</v>
+        <v>3709</v>
       </c>
       <c r="C4" t="n">
-        <v>7214</v>
+        <v>7660</v>
       </c>
       <c r="D4" t="n">
-        <v>12281</v>
+        <v>16236</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1832</v>
+        <v>1905</v>
       </c>
       <c r="C5" t="n">
-        <v>7557</v>
+        <v>8559</v>
       </c>
       <c r="D5" t="n">
-        <v>4571</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>795</v>
+        <v>893</v>
       </c>
       <c r="C6" t="n">
-        <v>5520</v>
+        <v>5005</v>
       </c>
       <c r="D6" t="n">
-        <v>1252</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>3145</v>
+        <v>2589</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1226</v>
+        <v>975</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3822</v>
+        <v>3649</v>
       </c>
       <c r="C2" t="n">
-        <v>7727</v>
+        <v>6011</v>
       </c>
       <c r="D2" t="n">
-        <v>14000</v>
+        <v>20725</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3314</v>
+        <v>3862</v>
       </c>
       <c r="C3" t="n">
-        <v>3842</v>
+        <v>4081</v>
       </c>
       <c r="D3" t="n">
-        <v>15488</v>
+        <v>20535</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3565</v>
+        <v>3636</v>
       </c>
       <c r="C4" t="n">
-        <v>6300</v>
+        <v>6538</v>
       </c>
       <c r="D4" t="n">
-        <v>12700</v>
+        <v>16719</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2288</v>
+        <v>2306</v>
       </c>
       <c r="C5" t="n">
-        <v>7320</v>
+        <v>8083</v>
       </c>
       <c r="D5" t="n">
-        <v>5542</v>
+        <v>7662</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1068</v>
+        <v>1146</v>
       </c>
       <c r="C6" t="n">
-        <v>6365</v>
+        <v>6409</v>
       </c>
       <c r="D6" t="n">
-        <v>1681</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>4136</v>
+        <v>3513</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1926</v>
+        <v>1547</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>598</v>
+        <v>491</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
+        <v>124</v>
+      </c>
+      <c r="D11" t="n">
         <v>131</v>
-      </c>
-      <c r="D11" t="n">
-        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" t="n">
         <v>45</v>
-      </c>
-      <c r="D14" t="n">
-        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2768</v>
+        <v>2599</v>
       </c>
       <c r="C2" t="n">
-        <v>4136</v>
+        <v>4039</v>
       </c>
       <c r="D2" t="n">
-        <v>9838</v>
+        <v>15345</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3046</v>
+        <v>3332</v>
       </c>
       <c r="C3" t="n">
-        <v>4896</v>
+        <v>4370</v>
       </c>
       <c r="D3" t="n">
-        <v>14615</v>
+        <v>19472</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3216</v>
+        <v>3399</v>
       </c>
       <c r="C4" t="n">
-        <v>5322</v>
+        <v>5646</v>
       </c>
       <c r="D4" t="n">
-        <v>12783</v>
+        <v>16847</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2528</v>
+        <v>2515</v>
       </c>
       <c r="C5" t="n">
-        <v>7086</v>
+        <v>7628</v>
       </c>
       <c r="D5" t="n">
-        <v>6182</v>
+        <v>8532</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1264</v>
+        <v>1322</v>
       </c>
       <c r="C6" t="n">
-        <v>6919</v>
+        <v>7164</v>
       </c>
       <c r="D6" t="n">
-        <v>2043</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>4942</v>
+        <v>4405</v>
       </c>
       <c r="D7" t="n">
-        <v>725</v>
+        <v>812</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>2449</v>
+        <v>1986</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>679</v>
+        <v>540</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3442,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4524</v>
+        <v>4062</v>
       </c>
       <c r="C2" t="n">
-        <v>6596</v>
+        <v>11089</v>
       </c>
       <c r="D2" t="n">
-        <v>9930</v>
+        <v>21456</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2484</v>
+        <v>2601</v>
       </c>
       <c r="C3" t="n">
-        <v>4134</v>
+        <v>3790</v>
       </c>
       <c r="D3" t="n">
-        <v>13106</v>
+        <v>17794</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2744</v>
+        <v>2934</v>
       </c>
       <c r="C4" t="n">
-        <v>4984</v>
+        <v>5014</v>
       </c>
       <c r="D4" t="n">
-        <v>12658</v>
+        <v>16687</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2515</v>
+        <v>2576</v>
       </c>
       <c r="C5" t="n">
-        <v>6227</v>
+        <v>6708</v>
       </c>
       <c r="D5" t="n">
-        <v>6881</v>
+        <v>9228</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1565</v>
+        <v>1577</v>
       </c>
       <c r="C6" t="n">
-        <v>6992</v>
+        <v>7275</v>
       </c>
       <c r="D6" t="n">
-        <v>2533</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="C7" t="n">
-        <v>5656</v>
+        <v>5376</v>
       </c>
       <c r="D7" t="n">
-        <v>872</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>3303</v>
+        <v>2810</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1257</v>
+        <v>984</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3753,7 +3753,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5007</v>
+        <v>8234</v>
       </c>
       <c r="C2" t="n">
-        <v>9297</v>
+        <v>8644</v>
       </c>
       <c r="D2" t="n">
-        <v>11499</v>
+        <v>20316</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3270</v>
+        <v>2970</v>
       </c>
       <c r="C2" t="n">
-        <v>3799</v>
+        <v>6564</v>
       </c>
       <c r="D2" t="n">
-        <v>7387</v>
+        <v>15963</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3366</v>
+        <v>3483</v>
       </c>
       <c r="C3" t="n">
-        <v>5049</v>
+        <v>5701</v>
       </c>
       <c r="D3" t="n">
-        <v>13988</v>
+        <v>19565</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3726</v>
+        <v>3881</v>
       </c>
       <c r="C4" t="n">
-        <v>7154</v>
+        <v>7310</v>
       </c>
       <c r="D4" t="n">
-        <v>12952</v>
+        <v>16952</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1492</v>
+        <v>1480</v>
       </c>
       <c r="C5" t="n">
-        <v>9555</v>
+        <v>10031</v>
       </c>
       <c r="D5" t="n">
-        <v>6195</v>
+        <v>8296</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>6844</v>
+        <v>6551</v>
       </c>
       <c r="D6" t="n">
-        <v>1984</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>3236</v>
+        <v>2753</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1231</v>
+        <v>964</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6112</v>
+        <v>7579</v>
       </c>
       <c r="C2" t="n">
-        <v>4720</v>
+        <v>5310</v>
       </c>
       <c r="D2" t="n">
-        <v>16883</v>
+        <v>33379</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2128</v>
+        <v>3496</v>
       </c>
       <c r="C3" t="n">
-        <v>4685</v>
+        <v>4356</v>
       </c>
       <c r="D3" t="n">
-        <v>2571</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
         <v>154</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4773</v>
+        <v>6546</v>
       </c>
       <c r="C2" t="n">
-        <v>10657</v>
+        <v>5220</v>
       </c>
       <c r="D2" t="n">
-        <v>16816</v>
+        <v>42458</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3382</v>
+        <v>4581</v>
       </c>
       <c r="C3" t="n">
-        <v>4057</v>
+        <v>4222</v>
       </c>
       <c r="D3" t="n">
-        <v>4786</v>
+        <v>8719</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>958</v>
+        <v>1523</v>
       </c>
       <c r="C4" t="n">
-        <v>2789</v>
+        <v>2596</v>
       </c>
       <c r="D4" t="n">
-        <v>1699</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4963,10 +4963,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4980,7 +4980,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" t="n">
         <v>172</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4933</v>
+        <v>5730</v>
       </c>
       <c r="C2" t="n">
-        <v>6669</v>
+        <v>6955</v>
       </c>
       <c r="D2" t="n">
-        <v>21203</v>
+        <v>42147</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3340</v>
+        <v>4543</v>
       </c>
       <c r="C3" t="n">
-        <v>6626</v>
+        <v>4124</v>
       </c>
       <c r="D3" t="n">
-        <v>6366</v>
+        <v>13573</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1844</v>
+        <v>2574</v>
       </c>
       <c r="C4" t="n">
-        <v>3449</v>
+        <v>3447</v>
       </c>
       <c r="D4" t="n">
-        <v>2240</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>445</v>
+        <v>661</v>
       </c>
       <c r="C5" t="n">
-        <v>1620</v>
+        <v>1494</v>
       </c>
       <c r="D5" t="n">
-        <v>1241</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6729</v>
+        <v>7217</v>
       </c>
       <c r="C2" t="n">
-        <v>10089</v>
+        <v>12331</v>
       </c>
       <c r="D2" t="n">
-        <v>20794</v>
+        <v>43717</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3391</v>
+        <v>4191</v>
       </c>
       <c r="C3" t="n">
-        <v>5786</v>
+        <v>4825</v>
       </c>
       <c r="D3" t="n">
-        <v>8173</v>
+        <v>16753</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2173</v>
+        <v>2969</v>
       </c>
       <c r="C4" t="n">
-        <v>5085</v>
+        <v>3693</v>
       </c>
       <c r="D4" t="n">
-        <v>2924</v>
+        <v>4795</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>937</v>
+        <v>1319</v>
       </c>
       <c r="C5" t="n">
-        <v>2534</v>
+        <v>2456</v>
       </c>
       <c r="D5" t="n">
-        <v>1363</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>260</v>
+        <v>337</v>
       </c>
       <c r="C6" t="n">
-        <v>954</v>
+        <v>886</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7722</v>
+        <v>6943</v>
       </c>
       <c r="C2" t="n">
-        <v>6703</v>
+        <v>6899</v>
       </c>
       <c r="D2" t="n">
-        <v>34377</v>
+        <v>37849</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3631</v>
+        <v>4053</v>
       </c>
       <c r="C3" t="n">
-        <v>6541</v>
+        <v>6982</v>
       </c>
       <c r="D3" t="n">
-        <v>8952</v>
+        <v>18310</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1727</v>
+        <v>2183</v>
       </c>
       <c r="C4" t="n">
-        <v>4481</v>
+        <v>3509</v>
       </c>
       <c r="D4" t="n">
-        <v>3308</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>801</v>
+        <v>1098</v>
       </c>
       <c r="C5" t="n">
-        <v>2819</v>
+        <v>2221</v>
       </c>
       <c r="D5" t="n">
-        <v>1278</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>281</v>
+        <v>383</v>
       </c>
       <c r="C6" t="n">
-        <v>1162</v>
+        <v>1108</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>786</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5620</v>
+        <v>6023</v>
       </c>
       <c r="C2" t="n">
-        <v>5272</v>
+        <v>7334</v>
       </c>
       <c r="D2" t="n">
-        <v>40658</v>
+        <v>36180</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4697</v>
+        <v>4524</v>
       </c>
       <c r="C3" t="n">
-        <v>5701</v>
+        <v>5980</v>
       </c>
       <c r="D3" t="n">
-        <v>12564</v>
+        <v>20244</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2329</v>
+        <v>2709</v>
       </c>
       <c r="C4" t="n">
-        <v>5633</v>
+        <v>5469</v>
       </c>
       <c r="D4" t="n">
-        <v>4313</v>
+        <v>8156</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1127</v>
+        <v>1438</v>
       </c>
       <c r="C5" t="n">
-        <v>3733</v>
+        <v>2904</v>
       </c>
       <c r="D5" t="n">
-        <v>1648</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>500</v>
+        <v>678</v>
       </c>
       <c r="C6" t="n">
-        <v>2086</v>
+        <v>1703</v>
       </c>
       <c r="D6" t="n">
-        <v>862</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="C7" t="n">
-        <v>831</v>
+        <v>769</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5497</v>
+        <v>4942</v>
       </c>
       <c r="C2" t="n">
-        <v>7592</v>
+        <v>7119</v>
       </c>
       <c r="D2" t="n">
-        <v>30538</v>
+        <v>34261</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4239</v>
+        <v>4307</v>
       </c>
       <c r="C3" t="n">
-        <v>4744</v>
+        <v>5811</v>
       </c>
       <c r="D3" t="n">
-        <v>16154</v>
+        <v>21241</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2972</v>
+        <v>3081</v>
       </c>
       <c r="C4" t="n">
-        <v>5553</v>
+        <v>5629</v>
       </c>
       <c r="D4" t="n">
-        <v>5766</v>
+        <v>10112</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1505</v>
+        <v>1782</v>
       </c>
       <c r="C5" t="n">
-        <v>4676</v>
+        <v>4145</v>
       </c>
       <c r="D5" t="n">
-        <v>2083</v>
+        <v>3319</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>727</v>
+        <v>947</v>
       </c>
       <c r="C6" t="n">
-        <v>2895</v>
+        <v>2295</v>
       </c>
       <c r="D6" t="n">
-        <v>977</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="C7" t="n">
-        <v>1482</v>
+        <v>1235</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>577</v>
+        <v>525</v>
       </c>
       <c r="D8" t="n">
         <v>405</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>28</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_16_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6208</v>
+        <v>3539</v>
       </c>
       <c r="C2" t="n">
-        <v>12423</v>
+        <v>9106</v>
       </c>
       <c r="D2" t="n">
-        <v>35038</v>
+        <v>30618</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3791</v>
+        <v>3043</v>
       </c>
       <c r="C3" t="n">
-        <v>5638</v>
+        <v>5809</v>
       </c>
       <c r="D3" t="n">
-        <v>21584</v>
+        <v>14247</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3126</v>
+        <v>2545</v>
       </c>
       <c r="C4" t="n">
-        <v>5546</v>
+        <v>6102</v>
       </c>
       <c r="D4" t="n">
-        <v>11523</v>
+        <v>7179</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2064</v>
+        <v>1566</v>
       </c>
       <c r="C5" t="n">
-        <v>4771</v>
+        <v>5530</v>
       </c>
       <c r="D5" t="n">
-        <v>4326</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1192</v>
+        <v>834</v>
       </c>
       <c r="C6" t="n">
-        <v>3102</v>
+        <v>3458</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>562</v>
+        <v>390</v>
       </c>
       <c r="C7" t="n">
-        <v>1722</v>
+        <v>1703</v>
       </c>
       <c r="D7" t="n">
-        <v>695</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>832</v>
+        <v>753</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>334</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8165</v>
+        <v>4400</v>
       </c>
       <c r="C2" t="n">
-        <v>7972</v>
+        <v>8235</v>
       </c>
       <c r="D2" t="n">
-        <v>29441</v>
+        <v>34061</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3907</v>
+        <v>2690</v>
       </c>
       <c r="C3" t="n">
-        <v>7539</v>
+        <v>6430</v>
       </c>
       <c r="D3" t="n">
-        <v>21890</v>
+        <v>15516</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2910</v>
+        <v>2363</v>
       </c>
       <c r="C4" t="n">
-        <v>5472</v>
+        <v>5834</v>
       </c>
       <c r="D4" t="n">
-        <v>12718</v>
+        <v>8114</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2232</v>
+        <v>1749</v>
       </c>
       <c r="C5" t="n">
-        <v>4960</v>
+        <v>5625</v>
       </c>
       <c r="D5" t="n">
-        <v>5189</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1402</v>
+        <v>1049</v>
       </c>
       <c r="C6" t="n">
-        <v>3748</v>
+        <v>4358</v>
       </c>
       <c r="D6" t="n">
-        <v>1867</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>728</v>
+        <v>515</v>
       </c>
       <c r="C7" t="n">
-        <v>2302</v>
+        <v>2459</v>
       </c>
       <c r="D7" t="n">
-        <v>788</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="C8" t="n">
-        <v>1181</v>
+        <v>1162</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C9" t="n">
-        <v>550</v>
+        <v>503</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9798</v>
+        <v>5886</v>
       </c>
       <c r="C2" t="n">
-        <v>8141</v>
+        <v>13206</v>
       </c>
       <c r="D2" t="n">
-        <v>43605</v>
+        <v>32219</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4449</v>
+        <v>2758</v>
       </c>
       <c r="C3" t="n">
-        <v>6940</v>
+        <v>6359</v>
       </c>
       <c r="D3" t="n">
-        <v>21605</v>
+        <v>16748</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2801</v>
+        <v>2159</v>
       </c>
       <c r="C4" t="n">
-        <v>6139</v>
+        <v>5914</v>
       </c>
       <c r="D4" t="n">
-        <v>13441</v>
+        <v>8855</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2224</v>
+        <v>1775</v>
       </c>
       <c r="C5" t="n">
-        <v>5010</v>
+        <v>5596</v>
       </c>
       <c r="D5" t="n">
-        <v>5993</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1561</v>
+        <v>1205</v>
       </c>
       <c r="C6" t="n">
-        <v>4145</v>
+        <v>4787</v>
       </c>
       <c r="D6" t="n">
-        <v>2289</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>878</v>
+        <v>648</v>
       </c>
       <c r="C7" t="n">
-        <v>2853</v>
+        <v>3196</v>
       </c>
       <c r="D7" t="n">
-        <v>909</v>
+        <v>822</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>402</v>
+        <v>295</v>
       </c>
       <c r="C8" t="n">
-        <v>1575</v>
+        <v>1669</v>
       </c>
       <c r="D8" t="n">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="C9" t="n">
-        <v>767</v>
+        <v>743</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8908</v>
+        <v>5326</v>
       </c>
       <c r="C2" t="n">
-        <v>5731</v>
+        <v>9085</v>
       </c>
       <c r="D2" t="n">
-        <v>36128</v>
+        <v>26579</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5115</v>
+        <v>3578</v>
       </c>
       <c r="C3" t="n">
-        <v>10095</v>
+        <v>10025</v>
       </c>
       <c r="D3" t="n">
-        <v>23754</v>
+        <v>17994</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2054</v>
+        <v>1640</v>
       </c>
       <c r="C4" t="n">
-        <v>8050</v>
+        <v>8608</v>
       </c>
       <c r="D4" t="n">
-        <v>12845</v>
+        <v>8532</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1442</v>
+        <v>1113</v>
       </c>
       <c r="C5" t="n">
-        <v>4062</v>
+        <v>4691</v>
       </c>
       <c r="D5" t="n">
-        <v>3796</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>811</v>
+        <v>598</v>
       </c>
       <c r="C6" t="n">
-        <v>2795</v>
+        <v>3132</v>
       </c>
       <c r="D6" t="n">
-        <v>890</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>371</v>
+        <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>1543</v>
+        <v>1635</v>
       </c>
       <c r="D7" t="n">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="D8" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>37</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5321</v>
+        <v>3270</v>
       </c>
       <c r="C2" t="n">
-        <v>2580</v>
+        <v>3922</v>
       </c>
       <c r="D2" t="n">
-        <v>25223</v>
+        <v>19192</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5671</v>
+        <v>3716</v>
       </c>
       <c r="C3" t="n">
-        <v>7479</v>
+        <v>8711</v>
       </c>
       <c r="D3" t="n">
-        <v>24007</v>
+        <v>18297</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2742</v>
+        <v>2084</v>
       </c>
       <c r="C4" t="n">
-        <v>9017</v>
+        <v>9329</v>
       </c>
       <c r="D4" t="n">
-        <v>14272</v>
+        <v>9717</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1575</v>
+        <v>1244</v>
       </c>
       <c r="C5" t="n">
-        <v>5742</v>
+        <v>6435</v>
       </c>
       <c r="D5" t="n">
-        <v>4795</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>953</v>
+        <v>713</v>
       </c>
       <c r="C6" t="n">
-        <v>3380</v>
+        <v>3861</v>
       </c>
       <c r="D6" t="n">
-        <v>1156</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>343</v>
+        <v>258</v>
       </c>
       <c r="C7" t="n">
-        <v>1970</v>
+        <v>2158</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
         <v>381</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6497</v>
+        <v>3085</v>
       </c>
       <c r="C2" t="n">
-        <v>7235</v>
+        <v>5963</v>
       </c>
       <c r="D2" t="n">
-        <v>25880</v>
+        <v>24417</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4692</v>
+        <v>2966</v>
       </c>
       <c r="C3" t="n">
-        <v>4673</v>
+        <v>5697</v>
       </c>
       <c r="D3" t="n">
-        <v>22789</v>
+        <v>17189</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3356</v>
+        <v>2398</v>
       </c>
       <c r="C4" t="n">
-        <v>8105</v>
+        <v>8832</v>
       </c>
       <c r="D4" t="n">
-        <v>15196</v>
+        <v>10821</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1824</v>
+        <v>1421</v>
       </c>
       <c r="C5" t="n">
-        <v>7155</v>
+        <v>7724</v>
       </c>
       <c r="D5" t="n">
-        <v>6104</v>
+        <v>4271</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1102</v>
+        <v>850</v>
       </c>
       <c r="C6" t="n">
-        <v>4346</v>
+        <v>4960</v>
       </c>
       <c r="D6" t="n">
-        <v>1664</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>504</v>
+        <v>382</v>
       </c>
       <c r="C7" t="n">
-        <v>2568</v>
+        <v>2912</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>1371</v>
+        <v>1468</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>35</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3915</v>
+        <v>1846</v>
       </c>
       <c r="C2" t="n">
-        <v>3520</v>
+        <v>2842</v>
       </c>
       <c r="D2" t="n">
-        <v>18057</v>
+        <v>17024</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4921</v>
+        <v>2889</v>
       </c>
       <c r="C3" t="n">
-        <v>5365</v>
+        <v>5565</v>
       </c>
       <c r="D3" t="n">
-        <v>22599</v>
+        <v>17555</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3709</v>
+        <v>2647</v>
       </c>
       <c r="C4" t="n">
-        <v>7660</v>
+        <v>8557</v>
       </c>
       <c r="D4" t="n">
-        <v>16236</v>
+        <v>11602</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1905</v>
+        <v>1484</v>
       </c>
       <c r="C5" t="n">
-        <v>8559</v>
+        <v>9116</v>
       </c>
       <c r="D5" t="n">
-        <v>6375</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>893</v>
+        <v>690</v>
       </c>
       <c r="C6" t="n">
-        <v>5005</v>
+        <v>5881</v>
       </c>
       <c r="D6" t="n">
-        <v>1585</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>2589</v>
+        <v>2904</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>975</v>
+        <v>1044</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3649</v>
+        <v>2094</v>
       </c>
       <c r="C2" t="n">
-        <v>6011</v>
+        <v>9931</v>
       </c>
       <c r="D2" t="n">
-        <v>20725</v>
+        <v>16603</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3862</v>
+        <v>2092</v>
       </c>
       <c r="C3" t="n">
-        <v>4081</v>
+        <v>3892</v>
       </c>
       <c r="D3" t="n">
-        <v>20535</v>
+        <v>16471</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3636</v>
+        <v>2425</v>
       </c>
       <c r="C4" t="n">
-        <v>6538</v>
+        <v>7000</v>
       </c>
       <c r="D4" t="n">
-        <v>16719</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2306</v>
+        <v>1735</v>
       </c>
       <c r="C5" t="n">
-        <v>8083</v>
+        <v>8767</v>
       </c>
       <c r="D5" t="n">
-        <v>7662</v>
+        <v>5397</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1146</v>
+        <v>896</v>
       </c>
       <c r="C6" t="n">
-        <v>6409</v>
+        <v>7221</v>
       </c>
       <c r="D6" t="n">
-        <v>2162</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>3513</v>
+        <v>4126</v>
       </c>
       <c r="D7" t="n">
-        <v>716</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1547</v>
+        <v>1720</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>491</v>
+        <v>524</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>32</v>
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2599</v>
+        <v>1586</v>
       </c>
       <c r="C2" t="n">
-        <v>4039</v>
+        <v>5081</v>
       </c>
       <c r="D2" t="n">
-        <v>15345</v>
+        <v>12872</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3332</v>
+        <v>1835</v>
       </c>
       <c r="C3" t="n">
-        <v>4370</v>
+        <v>5700</v>
       </c>
       <c r="D3" t="n">
-        <v>19472</v>
+        <v>15748</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3399</v>
+        <v>2128</v>
       </c>
       <c r="C4" t="n">
-        <v>5646</v>
+        <v>5765</v>
       </c>
       <c r="D4" t="n">
-        <v>16847</v>
+        <v>12447</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2515</v>
+        <v>1865</v>
       </c>
       <c r="C5" t="n">
-        <v>7628</v>
+        <v>8293</v>
       </c>
       <c r="D5" t="n">
-        <v>8532</v>
+        <v>5999</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1322</v>
+        <v>1041</v>
       </c>
       <c r="C6" t="n">
-        <v>7164</v>
+        <v>7987</v>
       </c>
       <c r="D6" t="n">
-        <v>2601</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>4405</v>
+        <v>5135</v>
       </c>
       <c r="D7" t="n">
-        <v>812</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1986</v>
+        <v>2250</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>540</v>
+        <v>602</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4062</v>
+        <v>1993</v>
       </c>
       <c r="C2" t="n">
-        <v>11089</v>
+        <v>7648</v>
       </c>
       <c r="D2" t="n">
-        <v>21456</v>
+        <v>15147</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2601</v>
+        <v>1472</v>
       </c>
       <c r="C3" t="n">
-        <v>3790</v>
+        <v>4907</v>
       </c>
       <c r="D3" t="n">
-        <v>17794</v>
+        <v>14395</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2934</v>
+        <v>1761</v>
       </c>
       <c r="C4" t="n">
-        <v>5014</v>
+        <v>5618</v>
       </c>
       <c r="D4" t="n">
-        <v>16687</v>
+        <v>12543</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2576</v>
+        <v>1804</v>
       </c>
       <c r="C5" t="n">
-        <v>6708</v>
+        <v>7125</v>
       </c>
       <c r="D5" t="n">
-        <v>9228</v>
+        <v>6683</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1577</v>
+        <v>1219</v>
       </c>
       <c r="C6" t="n">
-        <v>7275</v>
+        <v>8036</v>
       </c>
       <c r="D6" t="n">
-        <v>3307</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>518</v>
+        <v>419</v>
       </c>
       <c r="C7" t="n">
-        <v>5376</v>
+        <v>6167</v>
       </c>
       <c r="D7" t="n">
-        <v>1014</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>2810</v>
+        <v>3260</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>984</v>
+        <v>1118</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8234</v>
+        <v>4188</v>
       </c>
       <c r="C2" t="n">
-        <v>8644</v>
+        <v>5096</v>
       </c>
       <c r="D2" t="n">
-        <v>20316</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2970</v>
+        <v>1440</v>
       </c>
       <c r="C2" t="n">
-        <v>6564</v>
+        <v>4466</v>
       </c>
       <c r="D2" t="n">
-        <v>15963</v>
+        <v>11269</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3483</v>
+        <v>1998</v>
       </c>
       <c r="C3" t="n">
-        <v>5701</v>
+        <v>5938</v>
       </c>
       <c r="D3" t="n">
-        <v>19565</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3881</v>
+        <v>2548</v>
       </c>
       <c r="C4" t="n">
-        <v>7310</v>
+        <v>8142</v>
       </c>
       <c r="D4" t="n">
-        <v>16952</v>
+        <v>12802</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1480</v>
+        <v>1159</v>
       </c>
       <c r="C5" t="n">
-        <v>10031</v>
+        <v>10893</v>
       </c>
       <c r="D5" t="n">
-        <v>8296</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>478</v>
+        <v>387</v>
       </c>
       <c r="C6" t="n">
-        <v>6551</v>
+        <v>7539</v>
       </c>
       <c r="D6" t="n">
-        <v>2462</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>2753</v>
+        <v>3194</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>964</v>
+        <v>1095</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
         <v>34</v>
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7579</v>
+        <v>5584</v>
       </c>
       <c r="C2" t="n">
-        <v>5310</v>
+        <v>6287</v>
       </c>
       <c r="D2" t="n">
-        <v>33379</v>
+        <v>22772</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3496</v>
+        <v>1781</v>
       </c>
       <c r="C3" t="n">
-        <v>4356</v>
+        <v>2609</v>
       </c>
       <c r="D3" t="n">
-        <v>4052</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
         <v>154</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6546</v>
+        <v>4146</v>
       </c>
       <c r="C2" t="n">
-        <v>5220</v>
+        <v>4717</v>
       </c>
       <c r="D2" t="n">
-        <v>42458</v>
+        <v>22393</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4581</v>
+        <v>3021</v>
       </c>
       <c r="C3" t="n">
-        <v>4222</v>
+        <v>4044</v>
       </c>
       <c r="D3" t="n">
-        <v>8719</v>
+        <v>5503</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1523</v>
+        <v>807</v>
       </c>
       <c r="C4" t="n">
-        <v>2596</v>
+        <v>1571</v>
       </c>
       <c r="D4" t="n">
-        <v>1959</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4963,10 +4963,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4980,7 +4980,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="n">
         <v>172</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5730</v>
+        <v>3925</v>
       </c>
       <c r="C2" t="n">
-        <v>6955</v>
+        <v>11292</v>
       </c>
       <c r="D2" t="n">
-        <v>42147</v>
+        <v>22966</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4543</v>
+        <v>2937</v>
       </c>
       <c r="C3" t="n">
-        <v>4124</v>
+        <v>3818</v>
       </c>
       <c r="D3" t="n">
-        <v>13573</v>
+        <v>7809</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2574</v>
+        <v>1618</v>
       </c>
       <c r="C4" t="n">
-        <v>3447</v>
+        <v>2939</v>
       </c>
       <c r="D4" t="n">
-        <v>3113</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>661</v>
+        <v>392</v>
       </c>
       <c r="C5" t="n">
-        <v>1494</v>
+        <v>952</v>
       </c>
       <c r="D5" t="n">
-        <v>1300</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7217</v>
+        <v>5090</v>
       </c>
       <c r="C2" t="n">
-        <v>12331</v>
+        <v>10482</v>
       </c>
       <c r="D2" t="n">
-        <v>43717</v>
+        <v>18761</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4191</v>
+        <v>2802</v>
       </c>
       <c r="C3" t="n">
-        <v>4825</v>
+        <v>6671</v>
       </c>
       <c r="D3" t="n">
-        <v>16753</v>
+        <v>9563</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2969</v>
+        <v>1934</v>
       </c>
       <c r="C4" t="n">
-        <v>3693</v>
+        <v>3322</v>
       </c>
       <c r="D4" t="n">
-        <v>4795</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1319</v>
+        <v>823</v>
       </c>
       <c r="C5" t="n">
-        <v>2456</v>
+        <v>1981</v>
       </c>
       <c r="D5" t="n">
-        <v>1573</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="C6" t="n">
-        <v>886</v>
+        <v>629</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6943</v>
+        <v>5976</v>
       </c>
       <c r="C2" t="n">
-        <v>6899</v>
+        <v>9626</v>
       </c>
       <c r="D2" t="n">
-        <v>37849</v>
+        <v>25726</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4053</v>
+        <v>2878</v>
       </c>
       <c r="C3" t="n">
-        <v>6982</v>
+        <v>7060</v>
       </c>
       <c r="D3" t="n">
-        <v>18310</v>
+        <v>9679</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2183</v>
+        <v>1460</v>
       </c>
       <c r="C4" t="n">
-        <v>3509</v>
+        <v>4209</v>
       </c>
       <c r="D4" t="n">
-        <v>5814</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1098</v>
+        <v>716</v>
       </c>
       <c r="C5" t="n">
-        <v>2221</v>
+        <v>1965</v>
       </c>
       <c r="D5" t="n">
-        <v>1685</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>383</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>1108</v>
+        <v>878</v>
       </c>
       <c r="D6" t="n">
-        <v>786</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>383</v>
+        <v>313</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5882,10 +5882,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6023</v>
+        <v>5234</v>
       </c>
       <c r="C2" t="n">
-        <v>7334</v>
+        <v>6630</v>
       </c>
       <c r="D2" t="n">
-        <v>36180</v>
+        <v>31207</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4524</v>
+        <v>3686</v>
       </c>
       <c r="C3" t="n">
-        <v>5980</v>
+        <v>7368</v>
       </c>
       <c r="D3" t="n">
-        <v>20244</v>
+        <v>11775</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2709</v>
+        <v>1909</v>
       </c>
       <c r="C4" t="n">
-        <v>5469</v>
+        <v>5873</v>
       </c>
       <c r="D4" t="n">
-        <v>8156</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1438</v>
+        <v>965</v>
       </c>
       <c r="C5" t="n">
-        <v>2904</v>
+        <v>3259</v>
       </c>
       <c r="D5" t="n">
-        <v>2426</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>678</v>
+        <v>452</v>
       </c>
       <c r="C6" t="n">
-        <v>1703</v>
+        <v>1493</v>
       </c>
       <c r="D6" t="n">
-        <v>931</v>
+        <v>871</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>215</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>769</v>
+        <v>634</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6207,10 +6207,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4942</v>
+        <v>3700</v>
       </c>
       <c r="C2" t="n">
-        <v>7119</v>
+        <v>7285</v>
       </c>
       <c r="D2" t="n">
-        <v>34261</v>
+        <v>22214</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4307</v>
+        <v>3653</v>
       </c>
       <c r="C3" t="n">
-        <v>5811</v>
+        <v>6029</v>
       </c>
       <c r="D3" t="n">
-        <v>21241</v>
+        <v>14036</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3081</v>
+        <v>2400</v>
       </c>
       <c r="C4" t="n">
-        <v>5629</v>
+        <v>6597</v>
       </c>
       <c r="D4" t="n">
-        <v>10112</v>
+        <v>6039</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1782</v>
+        <v>1245</v>
       </c>
       <c r="C5" t="n">
-        <v>4145</v>
+        <v>4621</v>
       </c>
       <c r="D5" t="n">
-        <v>3319</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>947</v>
+        <v>644</v>
       </c>
       <c r="C6" t="n">
-        <v>2295</v>
+        <v>2393</v>
       </c>
       <c r="D6" t="n">
-        <v>1176</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>380</v>
+        <v>264</v>
       </c>
       <c r="C7" t="n">
-        <v>1235</v>
+        <v>1088</v>
       </c>
       <c r="D7" t="n">
-        <v>613</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>525</v>
+        <v>456</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_16_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3539</v>
+        <v>1074</v>
       </c>
       <c r="C2" t="n">
-        <v>9106</v>
+        <v>2789</v>
       </c>
       <c r="D2" t="n">
-        <v>30618</v>
+        <v>17601</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3043</v>
+        <v>2046</v>
       </c>
       <c r="C3" t="n">
-        <v>5809</v>
+        <v>6704</v>
       </c>
       <c r="D3" t="n">
-        <v>14247</v>
+        <v>17929</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2545</v>
+        <v>1539</v>
       </c>
       <c r="C4" t="n">
-        <v>6102</v>
+        <v>7253</v>
       </c>
       <c r="D4" t="n">
-        <v>7179</v>
+        <v>7498</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1566</v>
+        <v>847</v>
       </c>
       <c r="C5" t="n">
-        <v>5530</v>
+        <v>4667</v>
       </c>
       <c r="D5" t="n">
-        <v>2859</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>834</v>
+        <v>365</v>
       </c>
       <c r="C6" t="n">
-        <v>3458</v>
+        <v>2031</v>
       </c>
       <c r="D6" t="n">
-        <v>1206</v>
+        <v>752</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>390</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>1703</v>
+        <v>729</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>753</v>
+        <v>352</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>334</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4400</v>
+        <v>1424</v>
       </c>
       <c r="C2" t="n">
-        <v>8235</v>
+        <v>4025</v>
       </c>
       <c r="D2" t="n">
-        <v>34061</v>
+        <v>18704</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2690</v>
+        <v>1345</v>
       </c>
       <c r="C3" t="n">
-        <v>6430</v>
+        <v>4103</v>
       </c>
       <c r="D3" t="n">
-        <v>15516</v>
+        <v>16616</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2363</v>
+        <v>1549</v>
       </c>
       <c r="C4" t="n">
-        <v>5834</v>
+        <v>6806</v>
       </c>
       <c r="D4" t="n">
-        <v>8114</v>
+        <v>9172</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1749</v>
+        <v>1041</v>
       </c>
       <c r="C5" t="n">
-        <v>5625</v>
+        <v>5955</v>
       </c>
       <c r="D5" t="n">
-        <v>3408</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1049</v>
+        <v>521</v>
       </c>
       <c r="C6" t="n">
-        <v>4358</v>
+        <v>3319</v>
       </c>
       <c r="D6" t="n">
-        <v>1443</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>2459</v>
+        <v>1348</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>221</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1162</v>
+        <v>521</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>503</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5886</v>
+        <v>759</v>
       </c>
       <c r="C2" t="n">
-        <v>13206</v>
+        <v>1738</v>
       </c>
       <c r="D2" t="n">
-        <v>32219</v>
+        <v>12745</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2758</v>
+        <v>1326</v>
       </c>
       <c r="C3" t="n">
-        <v>6359</v>
+        <v>3908</v>
       </c>
       <c r="D3" t="n">
-        <v>16748</v>
+        <v>16441</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2159</v>
+        <v>1679</v>
       </c>
       <c r="C4" t="n">
-        <v>5914</v>
+        <v>6345</v>
       </c>
       <c r="D4" t="n">
-        <v>8855</v>
+        <v>10119</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1775</v>
+        <v>1058</v>
       </c>
       <c r="C5" t="n">
-        <v>5596</v>
+        <v>6884</v>
       </c>
       <c r="D5" t="n">
-        <v>3982</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1205</v>
+        <v>405</v>
       </c>
       <c r="C6" t="n">
-        <v>4787</v>
+        <v>4218</v>
       </c>
       <c r="D6" t="n">
-        <v>1674</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>648</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>3196</v>
+        <v>1283</v>
       </c>
       <c r="D7" t="n">
-        <v>822</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>295</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1669</v>
+        <v>485</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>743</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>345</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5326</v>
+        <v>841</v>
       </c>
       <c r="C2" t="n">
-        <v>9085</v>
+        <v>5628</v>
       </c>
       <c r="D2" t="n">
-        <v>26579</v>
+        <v>16897</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3578</v>
+        <v>917</v>
       </c>
       <c r="C3" t="n">
-        <v>10025</v>
+        <v>2490</v>
       </c>
       <c r="D3" t="n">
-        <v>17994</v>
+        <v>14879</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1640</v>
+        <v>1344</v>
       </c>
       <c r="C4" t="n">
-        <v>8608</v>
+        <v>5010</v>
       </c>
       <c r="D4" t="n">
-        <v>8532</v>
+        <v>10903</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1113</v>
+        <v>1207</v>
       </c>
       <c r="C5" t="n">
-        <v>4691</v>
+        <v>6543</v>
       </c>
       <c r="D5" t="n">
-        <v>2710</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C6" t="n">
-        <v>3132</v>
+        <v>5445</v>
       </c>
       <c r="D6" t="n">
-        <v>805</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>1635</v>
+        <v>2601</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>728</v>
+        <v>819</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D14" t="n">
         <v>67</v>
-      </c>
-      <c r="D14" t="n">
-        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3270</v>
+        <v>573</v>
       </c>
       <c r="C2" t="n">
-        <v>3922</v>
+        <v>3001</v>
       </c>
       <c r="D2" t="n">
-        <v>19192</v>
+        <v>12338</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3716</v>
+        <v>776</v>
       </c>
       <c r="C3" t="n">
-        <v>8711</v>
+        <v>3494</v>
       </c>
       <c r="D3" t="n">
-        <v>18297</v>
+        <v>14439</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2084</v>
+        <v>1109</v>
       </c>
       <c r="C4" t="n">
-        <v>9329</v>
+        <v>3888</v>
       </c>
       <c r="D4" t="n">
-        <v>9717</v>
+        <v>11248</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1244</v>
+        <v>1234</v>
       </c>
       <c r="C5" t="n">
-        <v>6435</v>
+        <v>6025</v>
       </c>
       <c r="D5" t="n">
-        <v>3406</v>
+        <v>5134</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="C6" t="n">
-        <v>3861</v>
+        <v>6112</v>
       </c>
       <c r="D6" t="n">
-        <v>1001</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>258</v>
+        <v>177</v>
       </c>
       <c r="C7" t="n">
-        <v>2158</v>
+        <v>3586</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>990</v>
+        <v>1243</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>381</v>
+        <v>429</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3085</v>
+        <v>1013</v>
       </c>
       <c r="C2" t="n">
-        <v>5963</v>
+        <v>4398</v>
       </c>
       <c r="D2" t="n">
-        <v>24417</v>
+        <v>16294</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2966</v>
+        <v>584</v>
       </c>
       <c r="C3" t="n">
-        <v>5697</v>
+        <v>2877</v>
       </c>
       <c r="D3" t="n">
-        <v>17189</v>
+        <v>13182</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2398</v>
+        <v>850</v>
       </c>
       <c r="C4" t="n">
-        <v>8832</v>
+        <v>3655</v>
       </c>
       <c r="D4" t="n">
-        <v>10821</v>
+        <v>11426</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1421</v>
+        <v>1100</v>
       </c>
       <c r="C5" t="n">
-        <v>7724</v>
+        <v>4935</v>
       </c>
       <c r="D5" t="n">
-        <v>4271</v>
+        <v>5917</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="C6" t="n">
-        <v>4960</v>
+        <v>6016</v>
       </c>
       <c r="D6" t="n">
-        <v>1334</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>382</v>
+        <v>332</v>
       </c>
       <c r="C7" t="n">
-        <v>2912</v>
+        <v>4684</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>795</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1468</v>
+        <v>2173</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>611</v>
+        <v>728</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1846</v>
+        <v>680</v>
       </c>
       <c r="C2" t="n">
-        <v>2842</v>
+        <v>2322</v>
       </c>
       <c r="D2" t="n">
-        <v>17024</v>
+        <v>11732</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2889</v>
+        <v>866</v>
       </c>
       <c r="C3" t="n">
-        <v>5565</v>
+        <v>3516</v>
       </c>
       <c r="D3" t="n">
-        <v>17555</v>
+        <v>14506</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2647</v>
+        <v>1430</v>
       </c>
       <c r="C4" t="n">
-        <v>8557</v>
+        <v>5229</v>
       </c>
       <c r="D4" t="n">
-        <v>11602</v>
+        <v>11726</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1484</v>
+        <v>863</v>
       </c>
       <c r="C5" t="n">
-        <v>9116</v>
+        <v>7880</v>
       </c>
       <c r="D5" t="n">
-        <v>4514</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>690</v>
+        <v>306</v>
       </c>
       <c r="C6" t="n">
-        <v>5881</v>
+        <v>6064</v>
       </c>
       <c r="D6" t="n">
-        <v>1306</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>2904</v>
+        <v>2129</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1044</v>
+        <v>713</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2094</v>
+        <v>367</v>
       </c>
       <c r="C2" t="n">
-        <v>9931</v>
+        <v>2219</v>
       </c>
       <c r="D2" t="n">
-        <v>16603</v>
+        <v>8683</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2092</v>
+        <v>663</v>
       </c>
       <c r="C3" t="n">
-        <v>3892</v>
+        <v>2613</v>
       </c>
       <c r="D3" t="n">
-        <v>16471</v>
+        <v>13066</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2425</v>
+        <v>984</v>
       </c>
       <c r="C4" t="n">
-        <v>7000</v>
+        <v>4096</v>
       </c>
       <c r="D4" t="n">
-        <v>12163</v>
+        <v>11360</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1735</v>
+        <v>788</v>
       </c>
       <c r="C5" t="n">
-        <v>8767</v>
+        <v>5891</v>
       </c>
       <c r="D5" t="n">
-        <v>5397</v>
+        <v>5678</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>896</v>
+        <v>302</v>
       </c>
       <c r="C6" t="n">
-        <v>7221</v>
+        <v>5629</v>
       </c>
       <c r="D6" t="n">
-        <v>1720</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>4126</v>
+        <v>2766</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1720</v>
+        <v>809</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>524</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>127</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1586</v>
+        <v>861</v>
       </c>
       <c r="C2" t="n">
-        <v>5081</v>
+        <v>4901</v>
       </c>
       <c r="D2" t="n">
-        <v>12872</v>
+        <v>12338</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1835</v>
+        <v>440</v>
       </c>
       <c r="C3" t="n">
-        <v>5700</v>
+        <v>2083</v>
       </c>
       <c r="D3" t="n">
-        <v>15748</v>
+        <v>11423</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2128</v>
+        <v>726</v>
       </c>
       <c r="C4" t="n">
-        <v>5765</v>
+        <v>3185</v>
       </c>
       <c r="D4" t="n">
-        <v>12447</v>
+        <v>11342</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1865</v>
+        <v>799</v>
       </c>
       <c r="C5" t="n">
-        <v>8293</v>
+        <v>4860</v>
       </c>
       <c r="D5" t="n">
-        <v>5999</v>
+        <v>6541</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1041</v>
+        <v>476</v>
       </c>
       <c r="C6" t="n">
-        <v>7987</v>
+        <v>5700</v>
       </c>
       <c r="D6" t="n">
-        <v>2067</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>228</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>5135</v>
+        <v>4222</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>802</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>2250</v>
+        <v>1737</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>602</v>
+        <v>510</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1993</v>
+        <v>832</v>
       </c>
       <c r="C2" t="n">
-        <v>7648</v>
+        <v>10189</v>
       </c>
       <c r="D2" t="n">
-        <v>15147</v>
+        <v>24412</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1472</v>
+        <v>519</v>
       </c>
       <c r="C3" t="n">
-        <v>4907</v>
+        <v>3057</v>
       </c>
       <c r="D3" t="n">
-        <v>14395</v>
+        <v>10768</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1761</v>
+        <v>517</v>
       </c>
       <c r="C4" t="n">
-        <v>5618</v>
+        <v>2527</v>
       </c>
       <c r="D4" t="n">
-        <v>12543</v>
+        <v>11011</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1804</v>
+        <v>701</v>
       </c>
       <c r="C5" t="n">
-        <v>7125</v>
+        <v>3922</v>
       </c>
       <c r="D5" t="n">
-        <v>6683</v>
+        <v>7062</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1219</v>
+        <v>570</v>
       </c>
       <c r="C6" t="n">
-        <v>8036</v>
+        <v>5237</v>
       </c>
       <c r="D6" t="n">
-        <v>2531</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>419</v>
+        <v>257</v>
       </c>
       <c r="C7" t="n">
-        <v>6167</v>
+        <v>4915</v>
       </c>
       <c r="D7" t="n">
-        <v>897</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>3260</v>
+        <v>2856</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1118</v>
+        <v>1038</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4188</v>
+        <v>7380</v>
       </c>
       <c r="C2" t="n">
-        <v>5096</v>
+        <v>10557</v>
       </c>
       <c r="D2" t="n">
-        <v>9362</v>
+        <v>13636</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1440</v>
+        <v>870</v>
       </c>
       <c r="C2" t="n">
-        <v>4466</v>
+        <v>11214</v>
       </c>
       <c r="D2" t="n">
-        <v>11269</v>
+        <v>19947</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1998</v>
+        <v>531</v>
       </c>
       <c r="C3" t="n">
-        <v>5938</v>
+        <v>5520</v>
       </c>
       <c r="D3" t="n">
-        <v>15510</v>
+        <v>11808</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2548</v>
+        <v>445</v>
       </c>
       <c r="C4" t="n">
-        <v>8142</v>
+        <v>2694</v>
       </c>
       <c r="D4" t="n">
-        <v>12802</v>
+        <v>10533</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1159</v>
+        <v>579</v>
       </c>
       <c r="C5" t="n">
-        <v>10893</v>
+        <v>3210</v>
       </c>
       <c r="D5" t="n">
-        <v>6076</v>
+        <v>7453</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>387</v>
+        <v>576</v>
       </c>
       <c r="C6" t="n">
-        <v>7539</v>
+        <v>4568</v>
       </c>
       <c r="D6" t="n">
-        <v>1980</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="C7" t="n">
-        <v>3194</v>
+        <v>5051</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>1095</v>
+        <v>3702</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>1740</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>594</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5584</v>
+        <v>5515</v>
       </c>
       <c r="C2" t="n">
-        <v>6287</v>
+        <v>10281</v>
       </c>
       <c r="D2" t="n">
-        <v>22772</v>
+        <v>22478</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1781</v>
+        <v>2377</v>
       </c>
       <c r="C3" t="n">
-        <v>2609</v>
+        <v>4169</v>
       </c>
       <c r="D3" t="n">
-        <v>2212</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4146</v>
+        <v>2653</v>
       </c>
       <c r="C2" t="n">
-        <v>4717</v>
+        <v>6128</v>
       </c>
       <c r="D2" t="n">
-        <v>22393</v>
+        <v>25435</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3021</v>
+        <v>3314</v>
       </c>
       <c r="C3" t="n">
-        <v>4044</v>
+        <v>6704</v>
       </c>
       <c r="D3" t="n">
-        <v>5503</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>807</v>
+        <v>1123</v>
       </c>
       <c r="C4" t="n">
-        <v>1571</v>
+        <v>2610</v>
       </c>
       <c r="D4" t="n">
-        <v>1627</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3925</v>
+        <v>2871</v>
       </c>
       <c r="C2" t="n">
-        <v>11292</v>
+        <v>3599</v>
       </c>
       <c r="D2" t="n">
-        <v>22966</v>
+        <v>27155</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2937</v>
+        <v>2465</v>
       </c>
       <c r="C3" t="n">
-        <v>3818</v>
+        <v>5485</v>
       </c>
       <c r="D3" t="n">
-        <v>7809</v>
+        <v>8677</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1618</v>
+        <v>1918</v>
       </c>
       <c r="C4" t="n">
-        <v>2939</v>
+        <v>4992</v>
       </c>
       <c r="D4" t="n">
-        <v>2321</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>392</v>
+        <v>526</v>
       </c>
       <c r="C5" t="n">
-        <v>952</v>
+        <v>1587</v>
       </c>
       <c r="D5" t="n">
-        <v>1218</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5090</v>
+        <v>2461</v>
       </c>
       <c r="C2" t="n">
-        <v>10482</v>
+        <v>5055</v>
       </c>
       <c r="D2" t="n">
-        <v>18761</v>
+        <v>33266</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2802</v>
+        <v>2196</v>
       </c>
       <c r="C3" t="n">
-        <v>6671</v>
+        <v>3857</v>
       </c>
       <c r="D3" t="n">
-        <v>9563</v>
+        <v>11008</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1934</v>
+        <v>1895</v>
       </c>
       <c r="C4" t="n">
-        <v>3322</v>
+        <v>5167</v>
       </c>
       <c r="D4" t="n">
-        <v>3229</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>823</v>
+        <v>1035</v>
       </c>
       <c r="C5" t="n">
-        <v>1981</v>
+        <v>3417</v>
       </c>
       <c r="D5" t="n">
-        <v>1382</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>236</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>629</v>
+        <v>959</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5976</v>
+        <v>2015</v>
       </c>
       <c r="C2" t="n">
-        <v>9626</v>
+        <v>7166</v>
       </c>
       <c r="D2" t="n">
-        <v>25726</v>
+        <v>40741</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2878</v>
+        <v>1915</v>
       </c>
       <c r="C3" t="n">
-        <v>7060</v>
+        <v>3890</v>
       </c>
       <c r="D3" t="n">
-        <v>9679</v>
+        <v>13616</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1460</v>
+        <v>1764</v>
       </c>
       <c r="C4" t="n">
-        <v>4209</v>
+        <v>4367</v>
       </c>
       <c r="D4" t="n">
-        <v>3713</v>
+        <v>4796</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>716</v>
+        <v>1255</v>
       </c>
       <c r="C5" t="n">
-        <v>1965</v>
+        <v>4203</v>
       </c>
       <c r="D5" t="n">
-        <v>1359</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>561</v>
       </c>
       <c r="C6" t="n">
-        <v>878</v>
+        <v>2175</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>313</v>
+        <v>620</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5234</v>
+        <v>2311</v>
       </c>
       <c r="C2" t="n">
-        <v>6630</v>
+        <v>10925</v>
       </c>
       <c r="D2" t="n">
-        <v>31207</v>
+        <v>31946</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3686</v>
+        <v>1623</v>
       </c>
       <c r="C3" t="n">
-        <v>7368</v>
+        <v>4810</v>
       </c>
       <c r="D3" t="n">
-        <v>11775</v>
+        <v>16715</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1909</v>
+        <v>1588</v>
       </c>
       <c r="C4" t="n">
-        <v>5873</v>
+        <v>4000</v>
       </c>
       <c r="D4" t="n">
-        <v>4860</v>
+        <v>6043</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>965</v>
+        <v>1311</v>
       </c>
       <c r="C5" t="n">
-        <v>3259</v>
+        <v>4194</v>
       </c>
       <c r="D5" t="n">
-        <v>1792</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>452</v>
+        <v>780</v>
       </c>
       <c r="C6" t="n">
-        <v>1493</v>
+        <v>3087</v>
       </c>
       <c r="D6" t="n">
-        <v>871</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>154</v>
+        <v>297</v>
       </c>
       <c r="C7" t="n">
-        <v>634</v>
+        <v>1314</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>272</v>
+        <v>441</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3700</v>
+        <v>2125</v>
       </c>
       <c r="C2" t="n">
-        <v>7285</v>
+        <v>6817</v>
       </c>
       <c r="D2" t="n">
-        <v>22214</v>
+        <v>25366</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3653</v>
+        <v>2459</v>
       </c>
       <c r="C3" t="n">
-        <v>6029</v>
+        <v>7922</v>
       </c>
       <c r="D3" t="n">
-        <v>14036</v>
+        <v>17918</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2400</v>
+        <v>1211</v>
       </c>
       <c r="C4" t="n">
-        <v>6597</v>
+        <v>6483</v>
       </c>
       <c r="D4" t="n">
-        <v>6039</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1245</v>
+        <v>720</v>
       </c>
       <c r="C5" t="n">
-        <v>4621</v>
+        <v>3025</v>
       </c>
       <c r="D5" t="n">
-        <v>2279</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>644</v>
+        <v>274</v>
       </c>
       <c r="C6" t="n">
-        <v>2393</v>
+        <v>1287</v>
       </c>
       <c r="D6" t="n">
-        <v>1026</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>1088</v>
+        <v>432</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>456</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
